--- a/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_64945_completo.xlsx
+++ b/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_64945_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R08a380e5324c4fbc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R631bb95673e74086"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,111 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.6995</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9626</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,72 +369,72 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      6.9363</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.1584</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.0191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      6.9501</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>13/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.1584</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>12/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.1236</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>11/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      7.0191</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
-          <x:t>10/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      6.9501</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>09/08/2026</x:t>
         </x:is>
       </x:c>
@@ -564,7 +669,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.1396</x:v>
+        <x:v>      7.0005</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -579,7 +684,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      7.0637</x:v>
+        <x:v>      6.7850</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,7 +804,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8323</x:v>
+        <x:v>      6.3810</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_64945_completo.xlsx
+++ b/13752_Cuenca_Pisco/_raw_reportes_xlsx/IDConfig_64945_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R631bb95673e74086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R9f9989fc37164d53"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,726 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2185</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6339</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.5018</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6204</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.6951</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7968</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.9698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.0618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.1063</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7131</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7651</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7735</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.8951</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      4.7152</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3790</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7613</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.9326</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.8328</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.7210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2853</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3738</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2484</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.2777</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      5.3830</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.4470</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.7285</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.8743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.9111</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.2447</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0214</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      7.5919</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.0585</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3950</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.5085</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.4704</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.3195</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.1698</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>23/08/2026</x:t>
         </x:is>
       </x:c>
@@ -279,7 +999,37 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      8.6995</x:v>
+        <x:v>      8.6841</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7763</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      8.7763</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -294,13 +1044,28 @@
         </x:is>
       </x:c>
       <x:c s="3">
+        <x:v>      8.6247</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
         <x:v>      8.1698</x:v>
       </x:c>
     </x:row>
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>18/08/2026</x:t>
+          <x:t>17/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -315,7 +1080,7 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>17/08/2026</x:t>
+          <x:t>16/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
@@ -330,21 +1095,6 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
-          <x:t>16/08/2026</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="7" t="inlineStr">
-        <x:is>
-          <x:t>00:00</x:t>
-        </x:is>
-      </x:c>
-      <x:c s="3">
-        <x:v>      8.1698</x:v>
-      </x:c>
-    </x:row>
-    <x:row>
-      <x:c s="1" t="inlineStr">
-        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1149,7 +1899,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      6.8455</x:v>
+        <x:v>      6.8501</x:v>
       </x:c>
     </x:row>
     <x:row>
